--- a/design/templates/generated/Uva/CATTLE_FLOOD_UVA_V1_upload_template.xlsx
+++ b/design/templates/generated/Uva/CATTLE_FLOOD_UVA_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -566,7 +566,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Livestock Sector / Cattle Farming - Flood - Uva Province   [profile CATTLE_FLOOD_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Livestock Sector / Cattle Farming - Flood - Uva Province   [profile CATTLE_FLOOD_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>UVA-001</t>
+          <t>BA1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -990,7 +990,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>UVA-002</t>
+          <t>BA2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -1034,7 +1034,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>UVA-003</t>
+          <t>BA3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -1078,7 +1078,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>UVA-004</t>
+          <t>BA4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -1122,12 +1122,12 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>UVA-005</t>
+          <t>BA5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Hali-Ela</t>
+          <t>Hali-ela</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -1166,7 +1166,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>UVA-006</t>
+          <t>BA6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1210,7 +1210,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>UVA-007</t>
+          <t>BA7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1254,7 +1254,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>UVA-008</t>
+          <t>BA8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1298,7 +1298,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>UVA-009</t>
+          <t>BA9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1342,7 +1342,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>UVA-010</t>
+          <t>BA10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1386,7 +1386,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>UVA-011</t>
+          <t>BA11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1430,7 +1430,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>UVA-012</t>
+          <t>BA12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1474,7 +1474,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>UVA-013</t>
+          <t>BA13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1518,7 +1518,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>UVA-014</t>
+          <t>BA14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1562,7 +1562,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>UVA-015</t>
+          <t>BA15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1606,7 +1606,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>UVA-016</t>
+          <t>MO1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1650,7 +1650,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>UVA-017</t>
+          <t>MO2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1694,7 +1694,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>UVA-018</t>
+          <t>MO3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1738,7 +1738,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>UVA-019</t>
+          <t>MO4</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1782,7 +1782,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>UVA-020</t>
+          <t>MO5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -1826,7 +1826,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>UVA-021</t>
+          <t>MO6</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -1870,7 +1870,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>UVA-022</t>
+          <t>MO7</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -1914,7 +1914,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>UVA-023</t>
+          <t>MO8</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -1958,7 +1958,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>UVA-024</t>
+          <t>MO9</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -2002,7 +2002,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>UVA-025</t>
+          <t>MO10</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -2046,7 +2046,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>UVA-026</t>
+          <t>MO11</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -2088,7 +2088,6 @@
       <c r="Z30" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
@@ -2141,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Livestock Sector / Cattle Farming - Flood - Uva Province   [profile CATTLE_FLOOD_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Livestock Sector / Cattle Farming - Flood - Uva Province   [profile CATTLE_FLOOD_UVA_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2444,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -2509,7 +2508,7 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
@@ -2521,7 +2520,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>UVA-001</t>
+          <t>BA1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -2535,7 +2534,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -2565,7 +2564,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>UVA-002</t>
+          <t>BA2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2579,7 +2578,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -2609,7 +2608,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>UVA-003</t>
+          <t>BA3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2623,7 +2622,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -2653,7 +2652,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>UVA-004</t>
+          <t>BA4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2667,7 +2666,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -2697,12 +2696,12 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>UVA-005</t>
+          <t>BA5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Hali-Ela</t>
+          <t>Hali-ela</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -2711,7 +2710,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -2741,7 +2740,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>UVA-006</t>
+          <t>BA6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2755,7 +2754,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -2785,7 +2784,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>UVA-007</t>
+          <t>BA7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -2799,7 +2798,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -2829,7 +2828,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>UVA-008</t>
+          <t>BA8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2843,7 +2842,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -2873,7 +2872,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>UVA-009</t>
+          <t>BA9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -2887,7 +2886,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -2917,7 +2916,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>UVA-010</t>
+          <t>BA10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2931,7 +2930,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -2961,7 +2960,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>UVA-011</t>
+          <t>BA11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -2975,7 +2974,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -3005,7 +3004,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>UVA-012</t>
+          <t>BA12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3019,7 +3018,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -3049,7 +3048,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>UVA-013</t>
+          <t>BA13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3063,7 +3062,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -3093,7 +3092,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>UVA-014</t>
+          <t>BA14</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3107,7 +3106,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -3137,7 +3136,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>UVA-015</t>
+          <t>BA15</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -3151,7 +3150,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -3181,7 +3180,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>UVA-016</t>
+          <t>MO1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -3195,7 +3194,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -3225,7 +3224,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>UVA-017</t>
+          <t>MO2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -3239,7 +3238,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -3269,7 +3268,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>UVA-018</t>
+          <t>MO3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -3283,7 +3282,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -3313,7 +3312,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>UVA-019</t>
+          <t>MO4</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -3327,7 +3326,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -3357,7 +3356,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>UVA-020</t>
+          <t>MO5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -3371,7 +3370,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -3401,7 +3400,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>UVA-021</t>
+          <t>MO6</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -3415,7 +3414,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -3445,7 +3444,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>UVA-022</t>
+          <t>MO7</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -3459,7 +3458,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -3489,7 +3488,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>UVA-023</t>
+          <t>MO8</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -3503,7 +3502,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -3533,7 +3532,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>UVA-024</t>
+          <t>MO9</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -3547,7 +3546,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -3577,7 +3576,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>UVA-025</t>
+          <t>MO10</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -3591,7 +3590,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -3621,7 +3620,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>UVA-026</t>
+          <t>MO11</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3635,7 +3634,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -3663,7 +3662,6 @@
       <c r="Z30" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
@@ -3682,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3691,6 +3689,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3738,6 +3737,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -3758,6 +3762,7 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -3786,6 +3791,7 @@
       <c r="F5" s="12" t="n">
         <v>100</v>
       </c>
+      <c r="G5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -3806,6 +3812,7 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="12" t="n"/>
+      <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -3826,6 +3833,7 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3846,6 +3854,7 @@
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
+      <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -3874,6 +3883,7 @@
       <c r="F9" s="12" t="n">
         <v>30</v>
       </c>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -3894,6 +3904,7 @@
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
+      <c r="G10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -3914,6 +3925,7 @@
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
+      <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -3942,6 +3954,7 @@
       <c r="F12" s="12" t="n">
         <v>30</v>
       </c>
+      <c r="G12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -3962,6 +3975,7 @@
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
+      <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -3982,6 +3996,7 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
+      <c r="G14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -4002,6 +4017,7 @@
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
+      <c r="G15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -4030,6 +4046,7 @@
       <c r="F16" s="12" t="n">
         <v>20</v>
       </c>
+      <c r="G16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -4050,6 +4067,7 @@
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
+      <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
@@ -4078,6 +4096,7 @@
       <c r="F18" s="12" t="n">
         <v>20</v>
       </c>
+      <c r="G18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -4098,6 +4117,7 @@
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
+      <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -4118,6 +4138,7 @@
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
+      <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -4138,6 +4159,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="12" t="n"/>
+      <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -4158,6 +4180,7 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="12" t="n"/>
+      <c r="G22" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -4182,9 +4205,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -4223,14 +4245,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: CATTLE_FLOOD_UVA_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: CATTLE_FLOOD_UVA_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -4244,14 +4266,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4287,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4921,80 +4943,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>19</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|CATTLE_FARMERS=average|CATTLE_FARMS=average|CATTLE_MILK_PRODUCTION_FARMS=average|CATTLE_POPULATION=average|LIVESTOCK_FARMERS=average|MITCH_COWS_ANNUAL_MILK_PRODUCTION=average|MITCH_COWS_DAILY_MILK_PRODUCTION=average|MITCH_COWS_MONTHLY_MILK_PRODUCTION=average|PASTURE_FODDER_EXTENT_ACRE=average|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS=average|PCT_EXTENSIVE=average|PCT_INTENSIVE=average|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_SEMI_INTENSIVE=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|CATTLE_FARMERS=average|CATTLE_FARMS=average|CATTLE_MILK_PRODUCTION_FARMS=average|CATTLE_POPULATION=average|LIVESTOCK_FARMERS=average|MITCH_COWS_ANNUAL_MILK_PRODUCTION=average|MITCH_COWS_DAILY_MILK_PRODUCTION=average|MITCH_COWS_MONTHLY_MILK_PRODUCTION=average|PASTURE_FODDER_EXTENT_ACRE=average|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS=average|PCT_EXTENSIVE=average|PCT_INTENSIVE=average|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_SEMI_INTENSIVE=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|VERY_WET_DAYS|CATTLE_FARMERS|CATTLE_FARMS|CATTLE_MILK_PRODUCTION_FARMS|CATTLE_POPULATION|LIVESTOCK_FARMERS|MITCH_COWS_ANNUAL_MILK_PRODUCTION|MITCH_COWS_DAILY_MILK_PRODUCTION|MITCH_COWS_MONTHLY_MILK_PRODUCTION|PASTURE_FODDER_EXTENT_ACRE|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS|PCT_EXTENSIVE|PCT_INTENSIVE|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS|PCT_SEMI_INTENSIVE|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/Uva/CATTLE_FLOOD_UVA_V1_upload_template.xlsx
+++ b/design/templates/generated/Uva/CATTLE_FLOOD_UVA_V1_upload_template.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,10 @@
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,105 +602,125 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>FLOOD_EVENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>FLOOD_HAZARD_INDEX</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>VERY_WET_DAYS</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_FARMERS</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_FARMS</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_MILK_PRODUCTION_FARMS</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_POPULATION</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>LIVESTOCK_FARMERS</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>MITCH_COWS_ANNUAL_MILK_PRODUCTION</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>MITCH_COWS_DAILY_MILK_PRODUCTION</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>MITCH_COWS_MONTHLY_MILK_PRODUCTION</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>PASTURE_FODDER_EXTENT_ACRE</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>PCT_EXTENSIVE</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>PCT_INTENSIVE</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>PCT_SEMI_INTENSIVE</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>DATA_SOURCE</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -730,124 +754,148 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>hazard: No. of Flood events_ 1974-2004_25%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>hazard: No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: No. of Flood events_ 2005-2023_75%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>hazard: Flood Hazard Index
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>hazard: No. of lightning incidents  - 1974 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>hazard: Strong wind events - 1978 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: 3 day cumulative rain fall
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>hazard: Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: Very wet days (95th percentile)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>exposure: # of Cattle Farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>exposure: No.of Neat Cattle Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>exposure: No.of Neat Cattle Milk Production Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>exposure: Cattle Population
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>exposure: Total livestock farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>exposure: Annual Mitch Cows Milk Production (l)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>exposure: Daily Mitch Cows Milk Production (l)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>exposure: Mitch Cows' Monthly Milk Production (l)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>exposure: Pasture &amp; Fodder Extent (Acre)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Cattle Farmers from total livestock Operators
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Extensive
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Intensive
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>exposure: % livestock farmers from total Agricultural Operators
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Semi Intensive
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>origin of the numbers</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -932,12 +980,24 @@
       <c r="X4" s="6" t="n">
         <v>775</v>
       </c>
-      <c r="Y4" s="6" t="inlineStr">
+      <c r="Y4" s="6" t="n">
+        <v>812.5</v>
+      </c>
+      <c r="Z4" s="6" t="n">
+        <v>850</v>
+      </c>
+      <c r="AA4" s="6" t="n">
+        <v>887.5</v>
+      </c>
+      <c r="AB4" s="6" t="n">
+        <v>925</v>
+      </c>
+      <c r="AC4" s="6" t="inlineStr">
         <is>
           <t>Dept. report 2021-2025</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>example row</t>
         </is>
@@ -986,6 +1046,10 @@
       <c r="X5" s="8" t="n"/>
       <c r="Y5" s="8" t="n"/>
       <c r="Z5" s="8" t="n"/>
+      <c r="AA5" s="8" t="n"/>
+      <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1030,6 +1094,10 @@
       <c r="X6" s="8" t="n"/>
       <c r="Y6" s="8" t="n"/>
       <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1074,6 +1142,10 @@
       <c r="X7" s="8" t="n"/>
       <c r="Y7" s="8" t="n"/>
       <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1118,6 +1190,10 @@
       <c r="X8" s="8" t="n"/>
       <c r="Y8" s="8" t="n"/>
       <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1162,6 +1238,10 @@
       <c r="X9" s="8" t="n"/>
       <c r="Y9" s="8" t="n"/>
       <c r="Z9" s="8" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+      <c r="AB9" s="8" t="n"/>
+      <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1206,6 +1286,10 @@
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="8" t="n"/>
       <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1250,6 +1334,10 @@
       <c r="X11" s="8" t="n"/>
       <c r="Y11" s="8" t="n"/>
       <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1294,6 +1382,10 @@
       <c r="X12" s="8" t="n"/>
       <c r="Y12" s="8" t="n"/>
       <c r="Z12" s="8" t="n"/>
+      <c r="AA12" s="8" t="n"/>
+      <c r="AB12" s="8" t="n"/>
+      <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1338,6 +1430,10 @@
       <c r="X13" s="8" t="n"/>
       <c r="Y13" s="8" t="n"/>
       <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1382,6 +1478,10 @@
       <c r="X14" s="8" t="n"/>
       <c r="Y14" s="8" t="n"/>
       <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1426,6 +1526,10 @@
       <c r="X15" s="8" t="n"/>
       <c r="Y15" s="8" t="n"/>
       <c r="Z15" s="8" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+      <c r="AB15" s="8" t="n"/>
+      <c r="AC15" s="8" t="n"/>
+      <c r="AD15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1470,6 +1574,10 @@
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="n"/>
       <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1514,6 +1622,10 @@
       <c r="X17" s="8" t="n"/>
       <c r="Y17" s="8" t="n"/>
       <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1558,6 +1670,10 @@
       <c r="X18" s="8" t="n"/>
       <c r="Y18" s="8" t="n"/>
       <c r="Z18" s="8" t="n"/>
+      <c r="AA18" s="8" t="n"/>
+      <c r="AB18" s="8" t="n"/>
+      <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1602,6 +1718,10 @@
       <c r="X19" s="8" t="n"/>
       <c r="Y19" s="8" t="n"/>
       <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1646,6 +1766,10 @@
       <c r="X20" s="8" t="n"/>
       <c r="Y20" s="8" t="n"/>
       <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1690,6 +1814,10 @@
       <c r="X21" s="8" t="n"/>
       <c r="Y21" s="8" t="n"/>
       <c r="Z21" s="8" t="n"/>
+      <c r="AA21" s="8" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="8" t="n"/>
+      <c r="AD21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1734,6 +1862,10 @@
       <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="n"/>
       <c r="Z22" s="8" t="n"/>
+      <c r="AA22" s="8" t="n"/>
+      <c r="AB22" s="8" t="n"/>
+      <c r="AC22" s="8" t="n"/>
+      <c r="AD22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1778,6 +1910,10 @@
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="n"/>
       <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1822,6 +1958,10 @@
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="n"/>
       <c r="Z24" s="8" t="n"/>
+      <c r="AA24" s="8" t="n"/>
+      <c r="AB24" s="8" t="n"/>
+      <c r="AC24" s="8" t="n"/>
+      <c r="AD24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1866,6 +2006,10 @@
       <c r="X25" s="8" t="n"/>
       <c r="Y25" s="8" t="n"/>
       <c r="Z25" s="8" t="n"/>
+      <c r="AA25" s="8" t="n"/>
+      <c r="AB25" s="8" t="n"/>
+      <c r="AC25" s="8" t="n"/>
+      <c r="AD25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1910,6 +2054,10 @@
       <c r="X26" s="8" t="n"/>
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="8" t="n"/>
+      <c r="AA26" s="8" t="n"/>
+      <c r="AB26" s="8" t="n"/>
+      <c r="AC26" s="8" t="n"/>
+      <c r="AD26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1954,6 +2102,10 @@
       <c r="X27" s="8" t="n"/>
       <c r="Y27" s="8" t="n"/>
       <c r="Z27" s="8" t="n"/>
+      <c r="AA27" s="8" t="n"/>
+      <c r="AB27" s="8" t="n"/>
+      <c r="AC27" s="8" t="n"/>
+      <c r="AD27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1998,6 +2150,10 @@
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="8" t="n"/>
+      <c r="AA28" s="8" t="n"/>
+      <c r="AB28" s="8" t="n"/>
+      <c r="AC28" s="8" t="n"/>
+      <c r="AD28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2042,6 +2198,10 @@
       <c r="X29" s="8" t="n"/>
       <c r="Y29" s="8" t="n"/>
       <c r="Z29" s="8" t="n"/>
+      <c r="AA29" s="8" t="n"/>
+      <c r="AB29" s="8" t="n"/>
+      <c r="AC29" s="8" t="n"/>
+      <c r="AD29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -2086,13 +2246,17 @@
       <c r="X30" s="8" t="n"/>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
+      <c r="AA30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n"/>
+      <c r="AC30" s="8" t="n"/>
+      <c r="AD30" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -2106,7 +2270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2135,6 +2299,10 @@
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2172,105 +2340,125 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>FLOOD_EVENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>FLOOD_HAZARD_INDEX</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>VERY_WET_DAYS</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_FARMERS</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_FARMS</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_MILK_PRODUCTION_FARMS</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>CATTLE_POPULATION</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>LIVESTOCK_FARMERS</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>MITCH_COWS_ANNUAL_MILK_PRODUCTION</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="U2" s="4" t="inlineStr">
         <is>
           <t>MITCH_COWS_DAILY_MILK_PRODUCTION</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="V2" s="4" t="inlineStr">
         <is>
           <t>MITCH_COWS_MONTHLY_MILK_PRODUCTION</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>PASTURE_FODDER_EXTENT_ACRE</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>PCT_EXTENSIVE</t>
         </is>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>PCT_INTENSIVE</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>PCT_SEMI_INTENSIVE</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>DATA_SOURCE</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -2304,124 +2492,148 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>hazard: No. of Flood events_ 1974-2004_25%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>hazard: No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: No. of Flood events_ 2005-2023_75%
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>hazard: Flood Hazard Index
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>hazard: No. of lightning incidents  - 1974 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>hazard: Strong wind events - 1978 to 2023
 &gt;&gt; fixed window - same value on both period tabs</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: 3 day cumulative rain fall
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>hazard: Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>hazard: Very wet days (95th percentile)
+&gt;&gt; enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>exposure: # of Cattle Farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>exposure: No.of Neat Cattle Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>exposure: No.of Neat Cattle Milk Production Farms
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>exposure: Cattle Population
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>exposure: Total livestock farmers
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>exposure: Annual Mitch Cows Milk Production (l)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>exposure: Daily Mitch Cows Milk Production (l)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>exposure: Mitch Cows' Monthly Milk Production (l)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>exposure: Pasture &amp; Fodder Extent (Acre)
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Cattle Farmers from total livestock Operators
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Extensive
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Intensive
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>exposure: % livestock farmers from total Agricultural Operators
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr">
+      <c r="AB3" s="5" t="inlineStr">
         <is>
           <t>exposure: % Semi Intensive
 &gt;&gt; enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>origin of the numbers</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
@@ -2506,12 +2718,24 @@
       <c r="X4" s="6" t="n">
         <v>775</v>
       </c>
-      <c r="Y4" s="6" t="inlineStr">
+      <c r="Y4" s="6" t="n">
+        <v>812.5</v>
+      </c>
+      <c r="Z4" s="6" t="n">
+        <v>850</v>
+      </c>
+      <c r="AA4" s="6" t="n">
+        <v>887.5</v>
+      </c>
+      <c r="AB4" s="6" t="n">
+        <v>925</v>
+      </c>
+      <c r="AC4" s="6" t="inlineStr">
         <is>
           <t>Dept. report 2026-2030</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>example row</t>
         </is>
@@ -2560,6 +2784,10 @@
       <c r="X5" s="8" t="n"/>
       <c r="Y5" s="8" t="n"/>
       <c r="Z5" s="8" t="n"/>
+      <c r="AA5" s="8" t="n"/>
+      <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2604,6 +2832,10 @@
       <c r="X6" s="8" t="n"/>
       <c r="Y6" s="8" t="n"/>
       <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2648,6 +2880,10 @@
       <c r="X7" s="8" t="n"/>
       <c r="Y7" s="8" t="n"/>
       <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2692,6 +2928,10 @@
       <c r="X8" s="8" t="n"/>
       <c r="Y8" s="8" t="n"/>
       <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2736,6 +2976,10 @@
       <c r="X9" s="8" t="n"/>
       <c r="Y9" s="8" t="n"/>
       <c r="Z9" s="8" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+      <c r="AB9" s="8" t="n"/>
+      <c r="AC9" s="8" t="n"/>
+      <c r="AD9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2780,6 +3024,10 @@
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="8" t="n"/>
       <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2824,6 +3072,10 @@
       <c r="X11" s="8" t="n"/>
       <c r="Y11" s="8" t="n"/>
       <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2868,6 +3120,10 @@
       <c r="X12" s="8" t="n"/>
       <c r="Y12" s="8" t="n"/>
       <c r="Z12" s="8" t="n"/>
+      <c r="AA12" s="8" t="n"/>
+      <c r="AB12" s="8" t="n"/>
+      <c r="AC12" s="8" t="n"/>
+      <c r="AD12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2912,6 +3168,10 @@
       <c r="X13" s="8" t="n"/>
       <c r="Y13" s="8" t="n"/>
       <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2956,6 +3216,10 @@
       <c r="X14" s="8" t="n"/>
       <c r="Y14" s="8" t="n"/>
       <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -3000,6 +3264,10 @@
       <c r="X15" s="8" t="n"/>
       <c r="Y15" s="8" t="n"/>
       <c r="Z15" s="8" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+      <c r="AB15" s="8" t="n"/>
+      <c r="AC15" s="8" t="n"/>
+      <c r="AD15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -3044,6 +3312,10 @@
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="n"/>
       <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -3088,6 +3360,10 @@
       <c r="X17" s="8" t="n"/>
       <c r="Y17" s="8" t="n"/>
       <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -3132,6 +3408,10 @@
       <c r="X18" s="8" t="n"/>
       <c r="Y18" s="8" t="n"/>
       <c r="Z18" s="8" t="n"/>
+      <c r="AA18" s="8" t="n"/>
+      <c r="AB18" s="8" t="n"/>
+      <c r="AC18" s="8" t="n"/>
+      <c r="AD18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -3176,6 +3456,10 @@
       <c r="X19" s="8" t="n"/>
       <c r="Y19" s="8" t="n"/>
       <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -3220,6 +3504,10 @@
       <c r="X20" s="8" t="n"/>
       <c r="Y20" s="8" t="n"/>
       <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -3264,6 +3552,10 @@
       <c r="X21" s="8" t="n"/>
       <c r="Y21" s="8" t="n"/>
       <c r="Z21" s="8" t="n"/>
+      <c r="AA21" s="8" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="8" t="n"/>
+      <c r="AD21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3308,6 +3600,10 @@
       <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="n"/>
       <c r="Z22" s="8" t="n"/>
+      <c r="AA22" s="8" t="n"/>
+      <c r="AB22" s="8" t="n"/>
+      <c r="AC22" s="8" t="n"/>
+      <c r="AD22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -3352,6 +3648,10 @@
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="n"/>
       <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -3396,6 +3696,10 @@
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="n"/>
       <c r="Z24" s="8" t="n"/>
+      <c r="AA24" s="8" t="n"/>
+      <c r="AB24" s="8" t="n"/>
+      <c r="AC24" s="8" t="n"/>
+      <c r="AD24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -3440,6 +3744,10 @@
       <c r="X25" s="8" t="n"/>
       <c r="Y25" s="8" t="n"/>
       <c r="Z25" s="8" t="n"/>
+      <c r="AA25" s="8" t="n"/>
+      <c r="AB25" s="8" t="n"/>
+      <c r="AC25" s="8" t="n"/>
+      <c r="AD25" s="8" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -3484,6 +3792,10 @@
       <c r="X26" s="8" t="n"/>
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="8" t="n"/>
+      <c r="AA26" s="8" t="n"/>
+      <c r="AB26" s="8" t="n"/>
+      <c r="AC26" s="8" t="n"/>
+      <c r="AD26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3528,6 +3840,10 @@
       <c r="X27" s="8" t="n"/>
       <c r="Y27" s="8" t="n"/>
       <c r="Z27" s="8" t="n"/>
+      <c r="AA27" s="8" t="n"/>
+      <c r="AB27" s="8" t="n"/>
+      <c r="AC27" s="8" t="n"/>
+      <c r="AD27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -3572,6 +3888,10 @@
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="8" t="n"/>
+      <c r="AA28" s="8" t="n"/>
+      <c r="AB28" s="8" t="n"/>
+      <c r="AC28" s="8" t="n"/>
+      <c r="AD28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -3616,6 +3936,10 @@
       <c r="X29" s="8" t="n"/>
       <c r="Y29" s="8" t="n"/>
       <c r="Z29" s="8" t="n"/>
+      <c r="AA29" s="8" t="n"/>
+      <c r="AB29" s="8" t="n"/>
+      <c r="AC29" s="8" t="n"/>
+      <c r="AD29" s="8" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3660,13 +3984,17 @@
       <c r="X30" s="8" t="n"/>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
+      <c r="AA30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n"/>
+      <c r="AC30" s="8" t="n"/>
+      <c r="AD30" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 S5 S6 S7 S8 S9 S10 S11 S12 S13 S14 S15 S16 S17 S18 S19 S20 S21 S22 S23 S24 S25 S26 S27 S28 S29 S30 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 W5 W6 W7 W8 W9 W10 W11 W12 W13 W14 W15 W16 W17 W18 W19 W20 W21 W22 W23 W24 W25 W26 W27 W28 W29 W30 X5 X6 X7 X8 X9 X10 X11 X12 X13 X14 X15 X16 X17 X18 X19 X20 X21 X22 X23 X24 X25 X26 X27 X28 X29 X30 Y5 Y6 Y7 Y8 Y9 Y10 Y11 Y12 Y13 Y14 Y15 Y16 Y17 Y18 Y19 Y20 Y21 Y22 Y23 Y24 Y25 Y26 Y27 Y28 Y29 Y30 Z5 Z6 Z7 Z8 Z9 Z10 Z11 Z12 Z13 Z14 Z15 Z16 Z17 Z18 Z19 Z20 Z21 Z22 Z23 Z24 Z25 Z26 Z27 Z28 Z29 Z30 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AB5 AB6 AB7 AB8 AB9 AB10 AB11 AB12 AB13 AB14 AB15 AB16 AB17 AB18 AB19 AB20 AB21 AB22 AB23 AB24 AB25 AB26 AB27 AB28 AB29 AB30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Raw values must be numbers &gt;= 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -3680,7 +4008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3746,12 +4074,12 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>FLOOD_EVENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
+          <t>No. of Flood events_ 1974-2004_25%</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -3765,43 +4093,35 @@
       <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>FLOOD_HAZARD_INDEX</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Flood Hazard Index</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>FLOOD_EVENTS_1974_TO_2023</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>No. of lightning incidents  - 1974 to 2023</t>
+          <t>No. of Flood events_ 2005-2023_75%</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -3815,35 +4135,43 @@
       <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Strong wind events - 1978 to 2023</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FLOOD_HAZARD_INDEX</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Flood Hazard Index</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="11" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>VERY_WET_DAYS</t>
+          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
+          <t>No. of lightning incidents  - 1974 to 2023</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3857,48 +4185,40 @@
       <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>CATTLE_FARMERS</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t># of Cattle Farmers</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr"/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Strong wind events - 1978 to 2023</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>CATTLE_FARMS</t>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>No.of Neat Cattle Farms</t>
+          <t>3 day cumulative rain fall</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -3909,17 +4229,17 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>CATTLE_MILK_PRODUCTION_FARMS</t>
+          <t>VERY_WET_DAYS</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>No.of Neat Cattle Milk Production Farms</t>
+          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -3928,64 +4248,64 @@
       <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>CATTLE_POPULATION</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Cattle Population</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Very wet days (95th percentile)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>CATTLE_FARMERS</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t># of Cattle Farmers</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E13" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>LIVESTOCK_FARMERS</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Total livestock farmers</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="11" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>MITCH_COWS_ANNUAL_MILK_PRODUCTION</t>
+          <t>CATTLE_FARMS</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Annual Mitch Cows Milk Production (l)</t>
+          <t>No.of Neat Cattle Farms</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -4001,12 +4321,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>MITCH_COWS_DAILY_MILK_PRODUCTION</t>
+          <t>CATTLE_MILK_PRODUCTION_FARMS</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Daily Mitch Cows Milk Production (l)</t>
+          <t>No.of Neat Cattle Milk Production Farms</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -4022,12 +4342,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>MITCH_COWS_MONTHLY_MILK_PRODUCTION</t>
+          <t>CATTLE_POPULATION</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Mitch Cows' Monthly Milk Production (l)</t>
+          <t>Cattle Population</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -4041,22 +4361,22 @@
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>PASTURE_FODDER_EXTENT_ACRE</t>
+          <t>LIVESTOCK_FARMERS</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Pasture &amp; Fodder Extent (Acre)</t>
+          <t>Total livestock farmers</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -4070,43 +4390,35 @@
       <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>% Cattle Farmers from total livestock Operators</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>MITCH_COWS_ANNUAL_MILK_PRODUCTION</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Annual Mitch Cows Milk Production (l)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PCT_EXTENSIVE</t>
+          <t>MITCH_COWS_DAILY_MILK_PRODUCTION</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>% Extensive</t>
+          <t>Daily Mitch Cows Milk Production (l)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -4120,35 +4432,43 @@
       <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>PCT_INTENSIVE</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>% Intensive</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>MITCH_COWS_MONTHLY_MILK_PRODUCTION</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Mitch Cows' Monthly Milk Production (l)</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="11" t="inlineStr"/>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS</t>
+          <t>PASTURE_FODDER_EXTENT_ACRE</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>% livestock farmers from total Agricultural Operators</t>
+          <t>Pasture &amp; Fodder Extent (Acre)</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -4162,45 +4482,137 @@
       <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>% Cattle Farmers from total livestock Operators</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>PCT_EXTENSIVE</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>% Extensive</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>PCT_INTENSIVE</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>% Intensive</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>% livestock farmers from total Agricultural Operators</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>PCT_SEMI_INTENSIVE</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>% Semi Intensive</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>SUM - hazard (must equal 100)</t>
         </is>
       </c>
-      <c r="F24" s="15">
-        <f>F4+F5+F6+F7+F8</f>
+      <c r="F28" s="15">
+        <f>F4+F5+F6+F7+F8+F9+F10+F11+F12</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>SUM - exposure (must equal 100)</t>
         </is>
       </c>
-      <c r="F25" s="15">
-        <f>F9+F10+F11+F12+F13+F14+F15+F16+F17+F18+F19+F20+F21+F22</f>
+      <c r="F29" s="15">
+        <f>F13+F14+F15+F16+F17+F18+F19+F20+F21+F22+F23+F24+F25+F26</f>
         <v/>
       </c>
     </row>
@@ -4209,7 +4621,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -4224,7 +4636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4245,7 +4657,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: CATTLE_FLOOD_UVA_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: CATTLE_FLOOD_UVA_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -4271,9 +4683,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4699,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4773,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>FLOOD_EVENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_1974_TO_2004</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
+          <t>No. of Flood events_ 1974-2004_25%</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -4378,19 +4790,19 @@
       <c r="E18" s="13" t="n"/>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>fixed window - same value on both period tabs</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>FLOOD_HAZARD_INDEX</t>
+          <t>FLOOD_EVENTS_1974_TO_2023</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>Flood Hazard Index</t>
+          <t>No. of Flood events - 1974 to 2023 (1974-2004, 25%, 2005 -2023, 75%)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -4398,14 +4810,8 @@
           <t>hazard</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>100</v>
-      </c>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
           <t>fixed window - same value on both period tabs</t>
@@ -4415,12 +4821,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
+          <t>FLOOD_EVENTS_2005_TO_2023</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>No. of lightning incidents  - 1974 to 2023</t>
+          <t>No. of Flood events_ 2005-2023_75%</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -4432,19 +4838,19 @@
       <c r="E20" s="13" t="n"/>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>fixed window - same value on both period tabs</t>
+          <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
+          <t>FLOOD_HAZARD_INDEX</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>Strong wind events - 1978 to 2023</t>
+          <t>Flood Hazard Index</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -4452,8 +4858,14 @@
           <t>hazard</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>100</v>
+      </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
           <t>fixed window - same value on both period tabs</t>
@@ -4463,12 +4875,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>VERY_WET_DAYS</t>
+          <t>LIGHTNING_INCIDENTS_1974_TO_2023</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
+          <t>No. of lightning incidents  - 1974 to 2023</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -4480,54 +4892,48 @@
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>enter a TYPICAL YEAR (not a total)</t>
+          <t>fixed window - same value on both period tabs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>CATTLE_FARMERS</t>
+          <t>STRONG_WIND_EVENTS_1978_TO_2023</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t># of Cattle Farmers</t>
+          <t>Strong wind events - 1978 to 2023</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>30</v>
-      </c>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>enter a TYPICAL YEAR (not a total)</t>
+          <t>fixed window - same value on both period tabs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>CATTLE_FARMS</t>
+          <t>THREE_DAY_CUMULATIVE_RAINFALL</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>No.of Neat Cattle Farms</t>
+          <t>3 day cumulative rain fall</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D24" s="13" t="n"/>
@@ -4541,17 +4947,17 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>CATTLE_MILK_PRODUCTION_FARMS</t>
+          <t>VERY_WET_DAYS</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>No.of Neat Cattle Milk Production Farms</t>
+          <t>Very wet days (95th percentile) and 3 day cumulative rain fall (out of 35 - 40% for very wet days and 60% for 3 day cumulative respectively)</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>hazard</t>
         </is>
       </c>
       <c r="D25" s="13" t="n"/>
@@ -4565,27 +4971,21 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>CATTLE_POPULATION</t>
+          <t>VERY_WET_DAYS_95TH_PERCENTILE</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Cattle Population</t>
+          <t>Very wet days (95th percentile)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>30</v>
-      </c>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
       <c r="F26" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -4595,12 +4995,12 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>LIVESTOCK_FARMERS</t>
+          <t>CATTLE_FARMERS</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Total livestock farmers</t>
+          <t># of Cattle Farmers</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -4608,8 +5008,14 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>30</v>
+      </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -4619,12 +5025,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>MITCH_COWS_ANNUAL_MILK_PRODUCTION</t>
+          <t>CATTLE_FARMS</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Annual Mitch Cows Milk Production (l)</t>
+          <t>No.of Neat Cattle Farms</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -4643,12 +5049,12 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>MITCH_COWS_DAILY_MILK_PRODUCTION</t>
+          <t>CATTLE_MILK_PRODUCTION_FARMS</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Daily Mitch Cows Milk Production (l)</t>
+          <t>No.of Neat Cattle Milk Production Farms</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -4667,12 +5073,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>MITCH_COWS_MONTHLY_MILK_PRODUCTION</t>
+          <t>CATTLE_POPULATION</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Mitch Cows' Monthly Milk Production (l)</t>
+          <t>Cattle Population</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -4686,7 +5092,7 @@
         </is>
       </c>
       <c r="E30" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
@@ -4697,12 +5103,12 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>PASTURE_FODDER_EXTENT_ACRE</t>
+          <t>LIVESTOCK_FARMERS</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Pasture &amp; Fodder Extent (Acre)</t>
+          <t>Total livestock farmers</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -4721,12 +5127,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS</t>
+          <t>MITCH_COWS_ANNUAL_MILK_PRODUCTION</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>% Cattle Farmers from total livestock Operators</t>
+          <t>Annual Mitch Cows Milk Production (l)</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -4734,14 +5140,8 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>20</v>
-      </c>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
       <c r="F32" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -4751,12 +5151,12 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>PCT_EXTENSIVE</t>
+          <t>MITCH_COWS_DAILY_MILK_PRODUCTION</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>% Extensive</t>
+          <t>Daily Mitch Cows Milk Production (l)</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -4775,12 +5175,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PCT_INTENSIVE</t>
+          <t>MITCH_COWS_MONTHLY_MILK_PRODUCTION</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>% Intensive</t>
+          <t>Mitch Cows' Monthly Milk Production (l)</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -4788,8 +5188,14 @@
           <t>exposure</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>20</v>
+      </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
@@ -4799,12 +5205,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS</t>
+          <t>PASTURE_FODDER_EXTENT_ACRE</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>% livestock farmers from total Agricultural Operators</t>
+          <t>Pasture &amp; Fodder Extent (Acre)</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -4823,22 +5229,124 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
+          <t>PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>% Cattle Farmers from total livestock Operators</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>PCT_EXTENSIVE</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>% Extensive</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>PCT_INTENSIVE</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>% Intensive</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>% livestock farmers from total Agricultural Operators</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>enter a TYPICAL YEAR (not a total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
           <t>PCT_SEMI_INTENSIVE</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>% Semi Intensive</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>exposure</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>enter a TYPICAL YEAR (not a total)</t>
         </is>
@@ -4948,7 +5456,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5468,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>0 add, 0 retire</t>
+          <t>4 add, 0 retire</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5480,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5515,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -5030,7 +5538,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|VERY_WET_DAYS=average|CATTLE_FARMERS=average|CATTLE_FARMS=average|CATTLE_MILK_PRODUCTION_FARMS=average|CATTLE_POPULATION=average|LIVESTOCK_FARMERS=average|MITCH_COWS_ANNUAL_MILK_PRODUCTION=average|MITCH_COWS_DAILY_MILK_PRODUCTION=average|MITCH_COWS_MONTHLY_MILK_PRODUCTION=average|PASTURE_FODDER_EXTENT_ACRE=average|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS=average|PCT_EXTENSIVE=average|PCT_INTENSIVE=average|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_SEMI_INTENSIVE=average</t>
+          <t>FLOOD_EVENTS_1974_TO_2004=average|FLOOD_EVENTS_1974_TO_2023=fixed_window|FLOOD_EVENTS_2005_TO_2023=average|FLOOD_HAZARD_INDEX=fixed_window|LIGHTNING_INCIDENTS_1974_TO_2023=fixed_window|STRONG_WIND_EVENTS_1978_TO_2023=fixed_window|THREE_DAY_CUMULATIVE_RAINFALL=average|VERY_WET_DAYS=average|VERY_WET_DAYS_95TH_PERCENTILE=average|CATTLE_FARMERS=average|CATTLE_FARMS=average|CATTLE_MILK_PRODUCTION_FARMS=average|CATTLE_POPULATION=average|LIVESTOCK_FARMERS=average|MITCH_COWS_ANNUAL_MILK_PRODUCTION=average|MITCH_COWS_DAILY_MILK_PRODUCTION=average|MITCH_COWS_MONTHLY_MILK_PRODUCTION=average|PASTURE_FODDER_EXTENT_ACRE=average|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS=average|PCT_EXTENSIVE=average|PCT_INTENSIVE=average|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS=average|PCT_SEMI_INTENSIVE=average</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5550,7 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|VERY_WET_DAYS|CATTLE_FARMERS|CATTLE_FARMS|CATTLE_MILK_PRODUCTION_FARMS|CATTLE_POPULATION|LIVESTOCK_FARMERS|MITCH_COWS_ANNUAL_MILK_PRODUCTION|MITCH_COWS_DAILY_MILK_PRODUCTION|MITCH_COWS_MONTHLY_MILK_PRODUCTION|PASTURE_FODDER_EXTENT_ACRE|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS|PCT_EXTENSIVE|PCT_INTENSIVE|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS|PCT_SEMI_INTENSIVE|DATA_SOURCE|NOTES</t>
+          <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|FLOOD_EVENTS_1974_TO_2004|FLOOD_EVENTS_1974_TO_2023|FLOOD_EVENTS_2005_TO_2023|FLOOD_HAZARD_INDEX|LIGHTNING_INCIDENTS_1974_TO_2023|STRONG_WIND_EVENTS_1978_TO_2023|THREE_DAY_CUMULATIVE_RAINFALL|VERY_WET_DAYS|VERY_WET_DAYS_95TH_PERCENTILE|CATTLE_FARMERS|CATTLE_FARMS|CATTLE_MILK_PRODUCTION_FARMS|CATTLE_POPULATION|LIVESTOCK_FARMERS|MITCH_COWS_ANNUAL_MILK_PRODUCTION|MITCH_COWS_DAILY_MILK_PRODUCTION|MITCH_COWS_MONTHLY_MILK_PRODUCTION|PASTURE_FODDER_EXTENT_ACRE|PCT_CATTLE_FARMERS_LIVESTOCK_OPERATORS|PCT_EXTENSIVE|PCT_INTENSIVE|PCT_LIVESTOCK_FARMERS_AGRICULTURAL_OPERATORS|PCT_SEMI_INTENSIVE|DATA_SOURCE|NOTES</t>
         </is>
       </c>
     </row>
